--- a/main/ig/StructureDefinition-fr-lm-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-human-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-human-name.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-human-name.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="103">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>Identifie le type de nom (ex : official, usual, etc.)</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>ValueSet HL7 name-use</t>
@@ -935,13 +938,13 @@
         <v>73</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>73</v>
@@ -976,10 +979,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1002,13 +1005,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1059,7 +1062,7 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>74</v>
@@ -1076,10 +1079,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1102,13 +1105,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1159,7 +1162,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -1176,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1202,13 +1205,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1259,7 +1262,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -1276,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1302,13 +1305,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1335,13 +1338,13 @@
         <v>73</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>73</v>
@@ -1359,7 +1362,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1376,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1402,13 +1405,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1435,13 +1438,13 @@
         <v>73</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>73</v>
@@ -1459,7 +1462,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1476,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1502,13 +1505,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1559,7 +1562,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
